--- a/data/liquidacion_final.xlsx
+++ b/data/liquidacion_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="112" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7211B230-F8C6-4C00-A445-C403EACD4BD1}"/>
+  <xr:revisionPtr revIDLastSave="113" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F33E1DC-4BA4-4591-99E6-7F49041DE8B2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F96EC60D-8A4F-416C-B913-DA3C0AB122B4}"/>
   </bookViews>
@@ -699,7 +699,7 @@
     <col min="4" max="4" width="43" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>

--- a/data/liquidacion_final.xlsx
+++ b/data/liquidacion_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="165" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1C6898F-447A-4D11-8C31-D8D9ACE49E28}"/>
+  <xr:revisionPtr revIDLastSave="192" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D84F4163-40AA-4172-8BDD-9F77A068D594}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F96EC60D-8A4F-416C-B913-DA3C0AB122B4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7732" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7772" uniqueCount="93">
   <si>
     <t>Sucursal</t>
   </si>
@@ -313,6 +313,12 @@
   <si>
     <t>Kelly Yuliana Ospina Saldarriaga</t>
   </si>
+  <si>
+    <t>Coordinador y Supervisora</t>
+  </si>
+  <si>
+    <t>GENERAL</t>
+  </si>
 </sst>
 </file>
 
@@ -347,10 +353,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5495,7 +5504,7 @@
         <v>9</v>
       </c>
       <c r="E185" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F185" t="s">
         <v>83</v>
@@ -9499,7 +9508,7 @@
         <v>9</v>
       </c>
       <c r="E339" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F339" t="s">
         <v>83</v>
@@ -9889,7 +9898,7 @@
         <v>9</v>
       </c>
       <c r="E354" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F354" t="s">
         <v>83</v>
@@ -11319,7 +11328,7 @@
         <v>9</v>
       </c>
       <c r="E409" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F409" t="s">
         <v>82</v>
@@ -11449,7 +11458,7 @@
         <v>9</v>
       </c>
       <c r="E414" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F414" t="s">
         <v>83</v>
@@ -11475,7 +11484,7 @@
         <v>9</v>
       </c>
       <c r="E415" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F415" t="s">
         <v>83</v>
@@ -11501,7 +11510,7 @@
         <v>9</v>
       </c>
       <c r="E416" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F416" t="s">
         <v>83</v>
@@ -11527,7 +11536,7 @@
         <v>9</v>
       </c>
       <c r="E417" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F417" t="s">
         <v>83</v>
@@ -11553,7 +11562,7 @@
         <v>9</v>
       </c>
       <c r="E418" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F418" t="s">
         <v>82</v>
@@ -11579,7 +11588,7 @@
         <v>9</v>
       </c>
       <c r="E419" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F419" t="s">
         <v>82</v>
@@ -11605,7 +11614,7 @@
         <v>9</v>
       </c>
       <c r="E420" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F420" t="s">
         <v>82</v>
@@ -11761,7 +11770,7 @@
         <v>9</v>
       </c>
       <c r="E426" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F426" t="s">
         <v>83</v>
@@ -11865,7 +11874,7 @@
         <v>9</v>
       </c>
       <c r="E430" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F430" t="s">
         <v>82</v>
@@ -18157,7 +18166,7 @@
         <v>9</v>
       </c>
       <c r="E672" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F672" t="s">
         <v>83</v>
@@ -18183,7 +18192,7 @@
         <v>9</v>
       </c>
       <c r="E673" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F673" t="s">
         <v>82</v>
@@ -22265,7 +22274,7 @@
         <v>9</v>
       </c>
       <c r="E830" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F830" t="s">
         <v>80</v>
@@ -22733,7 +22742,7 @@
         <v>9</v>
       </c>
       <c r="E848" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F848" t="s">
         <v>89</v>
@@ -22785,7 +22794,7 @@
         <v>9</v>
       </c>
       <c r="E850" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F850" t="s">
         <v>89</v>
@@ -23435,7 +23444,7 @@
         <v>9</v>
       </c>
       <c r="E875" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F875" t="s">
         <v>82</v>
@@ -26113,7 +26122,7 @@
         <v>9</v>
       </c>
       <c r="E978" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F978" t="s">
         <v>80</v>
@@ -26139,7 +26148,7 @@
         <v>9</v>
       </c>
       <c r="E979" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F979" t="s">
         <v>83</v>
@@ -50930,63 +50939,293 @@
       </c>
     </row>
     <row r="1933" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1933" s="2"/>
+      <c r="A1933" s="2">
+        <v>46056</v>
+      </c>
+      <c r="B1933" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1933">
+        <v>98667259</v>
+      </c>
+      <c r="D1933" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1933" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1933" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1933">
+        <v>31</v>
+      </c>
+      <c r="H1933" s="1">
+        <v>791.29999999999984</v>
+      </c>
     </row>
     <row r="1934" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1934" s="2"/>
+      <c r="A1934" s="2">
+        <v>46057</v>
+      </c>
+      <c r="B1934" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1934">
+        <v>98667259</v>
+      </c>
+      <c r="D1934" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1934" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1934" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1934">
+        <v>24.5</v>
+      </c>
+      <c r="H1934" s="1">
+        <v>363.27500000000009</v>
+      </c>
     </row>
     <row r="1935" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1935" s="2"/>
+      <c r="A1935" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B1935" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1935">
+        <v>98667259</v>
+      </c>
+      <c r="D1935" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1935" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1935" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1935">
+        <v>522</v>
+      </c>
+      <c r="H1935" s="1">
+        <v>870.25</v>
+      </c>
     </row>
     <row r="1936" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1936" s="2"/>
-    </row>
-    <row r="1937" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1937" s="2"/>
-    </row>
-    <row r="1938" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1938" s="2"/>
-    </row>
-    <row r="1939" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1939" s="2"/>
-    </row>
-    <row r="1940" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1940" s="2"/>
-    </row>
-    <row r="1941" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1941" s="2"/>
-    </row>
-    <row r="1942" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1942" s="2"/>
-    </row>
-    <row r="1943" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1936" s="2">
+        <v>46056</v>
+      </c>
+      <c r="B1936" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1936">
+        <v>98667259</v>
+      </c>
+      <c r="D1936" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1936" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1936" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1936">
+        <v>163</v>
+      </c>
+      <c r="H1936" s="1">
+        <v>1638.2400000000018</v>
+      </c>
+    </row>
+    <row r="1937" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1937" s="2">
+        <v>46059</v>
+      </c>
+      <c r="B1937" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1937">
+        <v>98667259</v>
+      </c>
+      <c r="D1937" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1937" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1937" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1937">
+        <v>199</v>
+      </c>
+      <c r="H1937" s="1">
+        <v>3469.2000000000098</v>
+      </c>
+    </row>
+    <row r="1938" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1938" s="2">
+        <v>46056</v>
+      </c>
+      <c r="B1938" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1938">
+        <v>98667259</v>
+      </c>
+      <c r="D1938" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1938" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1938" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1938">
+        <v>31</v>
+      </c>
+      <c r="H1938" s="1">
+        <v>791.29999999999984</v>
+      </c>
+    </row>
+    <row r="1939" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1939" s="2">
+        <v>46058</v>
+      </c>
+      <c r="B1939" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1939">
+        <v>98667259</v>
+      </c>
+      <c r="D1939" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1939" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1939" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1939">
+        <v>24.5</v>
+      </c>
+      <c r="H1939" s="1">
+        <v>363.27500000000009</v>
+      </c>
+    </row>
+    <row r="1940" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1940" s="2">
+        <v>46056</v>
+      </c>
+      <c r="B1940" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1940">
+        <v>98667259</v>
+      </c>
+      <c r="D1940" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1940" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1940" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1940">
+        <v>522</v>
+      </c>
+      <c r="H1940" s="1">
+        <v>870.25</v>
+      </c>
+    </row>
+    <row r="1941" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1941" s="2">
+        <v>46056</v>
+      </c>
+      <c r="B1941" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1941">
+        <v>98667259</v>
+      </c>
+      <c r="D1941" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1941" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1941" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1941">
+        <v>163</v>
+      </c>
+      <c r="H1941" s="1">
+        <v>1638.2400000000018</v>
+      </c>
+    </row>
+    <row r="1942" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1942" s="2">
+        <v>46056</v>
+      </c>
+      <c r="B1942" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1942">
+        <v>98667259</v>
+      </c>
+      <c r="D1942" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1942" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1942" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1942">
+        <v>199</v>
+      </c>
+      <c r="H1942" s="1">
+        <v>3469.2000000000098</v>
+      </c>
+    </row>
+    <row r="1943" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1943" s="2"/>
     </row>
-    <row r="1944" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1944" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1944" s="2"/>
     </row>
-    <row r="1945" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1945" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1945" s="2"/>
     </row>
-    <row r="1946" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1946" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1946" s="2"/>
     </row>
-    <row r="1947" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1947" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1947" s="2"/>
     </row>
-    <row r="1948" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1948" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1948" s="2"/>
     </row>
-    <row r="1949" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1949" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1949" s="2"/>
     </row>
-    <row r="1950" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1950" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1950" s="2"/>
     </row>
-    <row r="1951" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1951" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1951" s="2"/>
     </row>
-    <row r="1952" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1952" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1952" s="2"/>
     </row>
     <row r="1953" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/liquidacion_final.xlsx
+++ b/data/liquidacion_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="192" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D84F4163-40AA-4172-8BDD-9F77A068D594}"/>
+  <xr:revisionPtr revIDLastSave="204" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C3138BE-0EE8-4E66-AD2F-4BDEEED79961}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F96EC60D-8A4F-416C-B913-DA3C0AB122B4}"/>
   </bookViews>
@@ -51276,100 +51276,110 @@
     <row r="1968" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1968" s="2"/>
     </row>
-    <row r="1969" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1969" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1969" s="2"/>
     </row>
-    <row r="1970" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1970" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1970" s="2"/>
     </row>
-    <row r="1971" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1971" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1971" s="2"/>
     </row>
-    <row r="1972" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1972" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1972" s="2"/>
     </row>
-    <row r="1973" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1973" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1973" s="2"/>
     </row>
-    <row r="1974" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1974" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1974" s="2"/>
     </row>
-    <row r="1975" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1975" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1975" s="2"/>
     </row>
-    <row r="1976" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1976" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1976" s="2"/>
     </row>
-    <row r="1977" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1977" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1977" s="2"/>
     </row>
-    <row r="1978" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1978" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1978" s="2"/>
-    </row>
-    <row r="1979" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F1978" s="3"/>
+    </row>
+    <row r="1979" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1979" s="2"/>
-    </row>
-    <row r="1980" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F1979" s="3"/>
+    </row>
+    <row r="1980" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1980" s="2"/>
-    </row>
-    <row r="1981" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F1980" s="3"/>
+    </row>
+    <row r="1981" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1981" s="2"/>
-    </row>
-    <row r="1982" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F1981" s="3"/>
+    </row>
+    <row r="1982" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1982" s="2"/>
-    </row>
-    <row r="1983" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F1982" s="3"/>
+    </row>
+    <row r="1983" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1983" s="2"/>
-    </row>
-    <row r="1984" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F1983" s="3"/>
+    </row>
+    <row r="1984" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1984" s="2"/>
-    </row>
-    <row r="1985" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F1984" s="3"/>
+    </row>
+    <row r="1985" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1985" s="2"/>
-    </row>
-    <row r="1986" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F1985" s="3"/>
+    </row>
+    <row r="1986" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1986" s="2"/>
-    </row>
-    <row r="1987" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F1986" s="3"/>
+    </row>
+    <row r="1987" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1987" s="2"/>
-    </row>
-    <row r="1988" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F1987" s="3"/>
+    </row>
+    <row r="1988" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1988" s="2"/>
     </row>
-    <row r="1989" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1989" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1989" s="2"/>
     </row>
-    <row r="1990" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1990" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1990" s="2"/>
     </row>
-    <row r="1991" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1991" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1991" s="2"/>
     </row>
-    <row r="1992" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1992" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1992" s="2"/>
     </row>
-    <row r="1993" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1993" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1993" s="2"/>
     </row>
-    <row r="1994" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1994" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1994" s="2"/>
     </row>
-    <row r="1995" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1995" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1995" s="2"/>
     </row>
-    <row r="1996" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1996" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1996" s="2"/>
     </row>
-    <row r="1997" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1997" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1997" s="2"/>
     </row>
-    <row r="1998" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1998" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1998" s="2"/>
     </row>
-    <row r="1999" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1999" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1999" s="2"/>
     </row>
-    <row r="2000" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2000" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2000" s="2"/>
     </row>
     <row r="2001" spans="1:1" x14ac:dyDescent="0.25">
